--- a/Assets/ArtRes/Excel/SceneInfo.xlsx
+++ b/Assets/ArtRes/Excel/SceneInfo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Unity Ex\demo\DEAD RISING\Assets\ArtRes\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A282AB9E-769A-4F9F-B450-6359EE7EAC8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD57394E-3C70-4195-9CE4-E5884A4640C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1470" yWindow="4470" windowWidth="24130" windowHeight="9210" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>id</t>
   </si>
@@ -75,6 +75,14 @@
   </si>
   <si>
     <t>SceneImg/GameScene3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>money</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>towerHp</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -445,7 +453,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.1796875" customWidth="1"/>
@@ -456,7 +464,7 @@
     <col min="7" max="7" width="15.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -472,8 +480,14 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -489,8 +503,14 @@
       <c r="E2" t="s">
         <v>7</v>
       </c>
+      <c r="F2">
+        <v>200</v>
+      </c>
+      <c r="G2">
+        <v>100</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -506,8 +526,14 @@
       <c r="E3" t="s">
         <v>10</v>
       </c>
+      <c r="F3">
+        <v>200</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -522,6 +548,12 @@
       </c>
       <c r="E4" t="s">
         <v>13</v>
+      </c>
+      <c r="F4">
+        <v>200</v>
+      </c>
+      <c r="G4">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
